--- a/plan-negocio/kit-arranque/PANEL_ARRANQUE_LEON_2026.xlsx
+++ b/plan-negocio/kit-arranque/PANEL_ARRANQUE_LEON_2026.xlsx
@@ -138,12 +138,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -605,7 +605,7 @@
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>Las cuotas son precio POR MES, no anuales.</t>
+          <t>Las cuotas son precio POR MES. Precios revisados con el mapa competitivo de León: mantenimiento 80 EUR (mercado 50-150) y web profesional 2.900 (un competidor local publica 2.500 en tienda online).</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>3500</v>
+        <v>2900</v>
       </c>
       <c r="C6" s="5" t="n">
         <v>600</v>
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>15</v>
@@ -721,7 +721,7 @@
       <c r="D13" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="H13" s="9" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>El escenario PESIMISTA es el que importa: si con él aguantas, el plan es robusto. El previsto son las 17 ventas del plan de negocio.</t>
         </is>
@@ -802,11 +802,11 @@
           <t>Previsto</t>
         </is>
       </c>
-      <c r="C19" s="10">
+      <c r="C19" s="9">
         <f>IF(B19="Pesimista",2,IF(B19="Optimista",4,3))</f>
         <v/>
       </c>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="H19" s="10" t="inlineStr">
         <is>
           <t>Escribe aquí: Pesimista, Previsto u Optimista.</t>
         </is>
@@ -872,11 +872,16 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Suministros (parte afecta de la vivienda)</t>
+          <t>Suministros (ver nota: NO es salida de caja)</t>
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>40</v>
+        <v>0</v>
+      </c>
+      <c r="H27" s="10" t="inlineStr">
+        <is>
+          <t>Los suministros de casa (luz, agua, internet) los pagas tengas negocio o no: son DEDUCCIÓN fiscal, no una salida de caja nueva. Por eso van a 0 aquí, aunque sí cuenten como gasto en el plan de negocio.</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -936,7 +941,7 @@
       <c r="B34" s="5" t="n">
         <v>179</v>
       </c>
-      <c r="H34" s="7" t="inlineStr">
+      <c r="H34" s="10" t="inlineStr">
         <is>
           <t>Lo que tienes el día 1. Es el número más importante de esta hoja.</t>
         </is>
@@ -951,7 +956,7 @@
       <c r="B35" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="H35" s="7" t="inlineStr">
+      <c r="H35" s="10" t="inlineStr">
         <is>
           <t>El resto se cobra al entregar, un mes después.</t>
         </is>
@@ -966,7 +971,7 @@
       <c r="B36" s="12" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="H36" s="7" t="inlineStr">
+      <c r="H36" s="10" t="inlineStr">
         <is>
           <t>7% si te das de alta en epígrafe PROFESIONAL (Secc. 2ª). Pon 0% si es empresarial.</t>
         </is>
@@ -981,7 +986,7 @@
       <c r="B37" s="12" t="n">
         <v>0.21</v>
       </c>
-      <c r="H37" s="7" t="inlineStr">
+      <c r="H37" s="10" t="inlineStr">
         <is>
           <t>Tipo general. No es tuyo: lo devuelves cada trimestre.</t>
         </is>
@@ -996,7 +1001,7 @@
       <c r="B38" s="12" t="n">
         <v>0.03</v>
       </c>
-      <c r="H38" s="7" t="inlineStr">
+      <c r="H38" s="10" t="inlineStr">
         <is>
           <t>Ventas que nunca llegas a cobrar. Un 3% es prudente en B2B pequeño.</t>
         </is>
@@ -1011,7 +1016,7 @@
       <c r="B39" s="12" t="n">
         <v>0.01</v>
       </c>
-      <c r="H39" s="7" t="inlineStr">
+      <c r="H39" s="10" t="inlineStr">
         <is>
           <t>Churn. Un 1% al mes es un 12% al año, que es lo normal.</t>
         </is>
@@ -1026,7 +1031,7 @@
       <c r="B40" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H40" s="7" t="inlineStr">
+      <c r="H40" s="10" t="inlineStr">
         <is>
           <t>Déjalo en 0 los primeros meses. Súbelo cuando la caja aguante.</t>
         </is>
@@ -1040,7 +1045,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="7" t="inlineStr">
+      <c r="A44" s="10" t="inlineStr">
         <is>
           <t>(rampa de arranque + agosto y diciembre flojos)</t>
         </is>
@@ -1162,9 +1167,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="H13:H17"/>
+    <mergeCell ref="H5:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3211,7 +3217,7 @@
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>Cambia "ESCENARIO ACTIVO" en la hoja Supuestos y apunta aquí el resultado. El libro recalcula solo, pero esta tabla es manual a propósito: sirve para comparar los tres de un vistazo.</t>
         </is>
@@ -3244,7 +3250,7 @@
       <c r="B6" s="5" t="n"/>
       <c r="C6" s="5" t="n"/>
       <c r="D6" s="5" t="n"/>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>← Rellena a mano tras probar cada escenario</t>
         </is>

--- a/plan-negocio/kit-arranque/PANEL_ARRANQUE_LEON_2026.xlsx
+++ b/plan-negocio/kit-arranque/PANEL_ARRANQUE_LEON_2026.xlsx
@@ -822,11 +822,11 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Suscripciones (Claude Pro, Adobe, SEO, hosting)</t>
+          <t>Suscripciones (Claude Pro + hosting)</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>119</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23">
